--- a/newdefect.xlsx
+++ b/newdefect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gwd.grpinf.net\AWSCloudDesktop\test-homedrives\AAJO.GWD\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76BC2216-929D-4962-A985-CE33130E5862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A3927A-8121-4CD6-8215-7659DA1CF7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13530" xr2:uid="{62731B7B-042D-4900-8AF1-52CFBD8960A6}"/>
   </bookViews>
@@ -169,6 +169,50 @@
         <a:xfrm>
           <a:off x="0" y="3810000"/>
           <a:ext cx="15642233" cy="3705742"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>78338</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>67189</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{181289C2-7F42-C21F-355D-E834345CA5ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7810500"/>
+          <a:ext cx="15318338" cy="3686689"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
